--- a/diseases/d026/2015-2019.xlsx
+++ b/diseases/d026/2015-2019.xlsx
@@ -1075,9 +1075,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -3409,9 +3406,6 @@
       <c r="O19" t="n">
         <v>4</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>1.191989236337196</v>
       </c>
@@ -5743,9 +5737,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -8077,9 +8068,6 @@
       <c r="O49" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.2834033339568207</v>
       </c>
@@ -10410,9 +10398,6 @@
       </c>
       <c r="O64" t="n">
         <v>1</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0.2772390868298958</v>

--- a/diseases/d026/2015-2019.xlsx
+++ b/diseases/d026/2015-2019.xlsx
@@ -938,28 +938,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1479,28 +1493,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1627,28 +1655,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1775,28 +1817,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -1923,28 +1979,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2071,28 +2141,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2219,28 +2303,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2367,28 +2465,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2515,28 +2627,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -2663,28 +2789,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -2811,28 +2951,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -2959,28 +3113,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3269,28 +3437,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -3810,28 +3992,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -3958,28 +4154,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4106,28 +4316,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -4254,28 +4478,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -4402,28 +4640,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -4550,28 +4802,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -4698,28 +4964,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -4846,28 +5126,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -4994,28 +5288,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -5142,28 +5450,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -5290,28 +5612,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -5600,28 +5936,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -6141,28 +6491,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -6289,28 +6653,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -6437,28 +6815,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -6585,28 +6977,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -6733,28 +7139,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -6881,28 +7301,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -7029,28 +7463,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -7177,28 +7625,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -7325,28 +7787,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -7473,28 +7949,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -7621,28 +8111,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -7931,28 +8435,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -8472,28 +8990,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -8620,28 +9152,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -8768,28 +9314,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -8916,28 +9476,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -9064,28 +9638,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -9212,28 +9800,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -9360,28 +9962,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -9508,28 +10124,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -9656,28 +10286,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -9804,28 +10448,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -9952,28 +10610,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -10262,28 +10934,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -10951,28 +11637,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -11099,28 +11799,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -11543,28 +12257,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -11987,28 +12715,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -12431,28 +13173,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -12875,28 +13631,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -13319,28 +14089,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -13763,28 +14547,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -14059,28 +14857,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -14355,28 +15167,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -14799,28 +15625,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
